--- a/DOSSIES_MULTIFORMATO/SEINFRA/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEINFRA/dossie.xlsx
@@ -636,12 +636,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022NE0002069</t>
+          <t>2022NE0002066</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1292.8</v>
+        <v>5879.68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -659,19 +659,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta SEINFRA.</t>
+          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2022NE0002070</t>
+          <t>2022NE0002067</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20914.51</v>
+        <v>2401.81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. nº042-2021-SEINFRA, destinados para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras E-Obras para a Secretaria de Infraestrutura e Região Met</t>
+          <t>Parte do Saldo do CT.019/2019-SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022NE0002067</t>
+          <t>2022NE0002070</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2401.81</v>
+        <v>20914.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -719,19 +719,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT.019/2019-SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. nº042-2021-SEINFRA, destinados para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras E-Obras para a Secretaria de Infraestrutura e Região Met</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022NE0002066</t>
+          <t>2022NE0002069</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5879.68</v>
+        <v>1292.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -749,17 +749,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
+          <t>CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020NE00748</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>2020NE00749</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19/2019</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>31/07/2020</t>
@@ -775,17 +779,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anulação total da NE n° 747/2020, em virtude de erro no Sistema AFI.</t>
+          <t>Termo aditivo ao CT. N° 019/2019-SEINFRA, Prestação de serviços de uso do Sistema de Gestão de Conteúdo Web para esta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020NE00746</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>2020NE00747</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19/2019</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>31/07/2020</t>
@@ -801,19 +809,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anulação Total da NE N. 744/2020 - SEINFRA, em virtude de descrição indevida.</t>
+          <t>Termo aditivo ao Contrato N°019/2020-SEINFRA - Prestação de serviços de uso do Sistema de Gestão de Conteúdo Web, para esta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020NE00759</t>
+          <t>2020NE00744</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -822,7 +830,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12729.59</v>
+        <v>7933.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -831,19 +839,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4º Termo Aditivo ao Contrato nº 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>1ª Termo aditivo ao CT. N°019/2019-SEINFRA - Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020NE00744</t>
+          <t>2020NE00759</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -852,7 +860,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7933.35</v>
+        <v>12729.59</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -861,21 +869,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1ª Termo aditivo ao CT. N°019/2019-SEINFRA - Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA</t>
+          <t>4º Termo Aditivo ao Contrato nº 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020NE00747</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>19/2019</t>
-        </is>
-      </c>
+          <t>2020NE00746</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>31/07/2020</t>
@@ -891,21 +895,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Termo aditivo ao Contrato N°019/2020-SEINFRA - Prestação de serviços de uso do Sistema de Gestão de Conteúdo Web, para esta SEINFRA.</t>
+          <t>Anulação Total da NE N. 744/2020 - SEINFRA, em virtude de descrição indevida.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020NE00749</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>19/2019</t>
-        </is>
-      </c>
+          <t>2020NE00748</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>31/07/2020</t>
@@ -921,7 +921,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Termo aditivo ao CT. N° 019/2019-SEINFRA, Prestação de serviços de uso do Sistema de Gestão de Conteúdo Web para esta SEINFRA.</t>
+          <t>Anulação total da NE n° 747/2020, em virtude de erro no Sistema AFI.</t>
         </is>
       </c>
     </row>
@@ -1078,17 +1078,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2016NE01172</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>2016NE01166</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>29/12/2016</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1250.66</v>
+        <v>7577.32</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1097,28 +1101,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°00053/2016, conforme Instrução Normativa N°01/2016, de 14 de Dezembro de 2016-SET/SEFAZ.</t>
+          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP ao Sistema de Administração Financeira Integrada - AFI ao</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2016NE01166</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01172</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>29/12/2016</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7577.32</v>
+        <v>1250.66</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP ao Sistema de Administração Financeira Integrada - AFI ao</t>
+          <t>Anulação parcial da NE N°00053/2016, conforme Instrução Normativa N°01/2016, de 14 de Dezembro de 2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023NE0000770</t>
+          <t>2023NE0000767</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4803.62</v>
+        <v>14242.04</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1247,19 +1247,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 019/2019 AD: 02.</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023NE0000767</t>
+          <t>2023NE0000770</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14242.04</v>
+        <v>4803.62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1277,14 +1277,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA.</t>
+          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 019/2019 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE01500</t>
+          <t>2018NE01499</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5185.28</v>
+        <v>2950.58</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 215/2018, referente ao Contrato n° 006/2018-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
+          <t>Anulação parcial da NE N° 211/2018, referente ao Contrato n° 001/2017-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE01507</t>
+          <t>2018NE01485</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8506.68</v>
+        <v>5470.32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1329,14 +1329,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anulação total da NE N° 869/2018, referente ao Contrato n° 059/2018-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
+          <t>Anulação parcial da NE N° 206/2018, referente ao Contrato n°021/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018NE01498</t>
+          <t>2018NE01476</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5550.23</v>
+        <v>615.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1355,14 +1355,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 210/2018, referente ao Contrato n° 011/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
+          <t>Anulação total da NE N°1042/2018, referente ao Contrato nº 009/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2018NE01480</t>
+          <t>2018NE01503</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8807.389999999999</v>
+        <v>26364.03</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anulação total da NE N°1124/2018, referente ao CT-00021/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
+          <t>Anulação parcial da NE N° 411/2018, referente ao Contrato n° 009/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2018NE01488</t>
+          <t>2018NE01506</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2950.58</v>
+        <v>6862.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anulação total da NE N° 207/2018, referente ao Contrato n°001/2017-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
+          <t>Anulação parcial da NE N° 801/2018, referente ao Contrato n° 011/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE01506</t>
+          <t>2018NE01488</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6862.4</v>
+        <v>2950.58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 801/2018, referente ao Contrato n° 011/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
+          <t>Anulação total da NE N° 207/2018, referente ao Contrato n°001/2017-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2018NE01503</t>
+          <t>2018NE01480</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26364.03</v>
+        <v>8807.389999999999</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 411/2018, referente ao Contrato n° 009/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
+          <t>Anulação total da NE N°1124/2018, referente ao CT-00021/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2018NE01476</t>
+          <t>2018NE01498</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>615.7</v>
+        <v>5550.23</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1511,14 +1511,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anulação total da NE N°1042/2018, referente ao Contrato nº 009/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
+          <t>Anulação parcial da NE N° 210/2018, referente ao Contrato n° 011/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2018NE01485</t>
+          <t>2018NE01507</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5470.32</v>
+        <v>8506.68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 206/2018, referente ao Contrato n°021/2016-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018</t>
+          <t>Anulação total da NE N° 869/2018, referente ao Contrato n° 059/2018-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/2018.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018NE01499</t>
+          <t>2018NE01500</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2950.58</v>
+        <v>5185.28</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N° 211/2018, referente ao Contrato n° 001/2017-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
+          <t>Anulação parcial da NE N° 215/2018, referente ao Contrato n° 006/2018-SEINFRA, em virtude do encerramento do exercício, conforme Instrução Normativa N°01/2018/SET/SEFAZ publicado no D.O.E em 30/11/201</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020NE01091</t>
+          <t>2020NE01087</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5797.1</v>
+        <v>35229.56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1593,19 +1593,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Saldo do Contrato N°009/2016-SEINFRA - Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo do Contrato N°021/2016-SEINFRA - Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020NE01089</t>
+          <t>2020NE01088</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>45353.4</v>
+        <v>18765.97</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1623,19 +1623,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Saldo do 4° Termo Aditivo ao Contrato N°009/2016-SEINFRA - Prestação de Serviços de Hospedagem do Sistema Integrado° de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo 2º Termo Aditivo ao Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020NE01084</t>
+          <t>2020NE01086</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5024.11</v>
+        <v>2659.04</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Saldo do Contrato N°011/2016-SEINFRA-Prestação de serviços para aquisição do Programa de execução de sistema de Protocolo em Plataforma WEB (sproweb) para Secretaria de Estado de Infraestrutura - SEIN</t>
+          <t>Saldo do CT. N°006/2018-SEINFRA - Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020NE01086</t>
+          <t>2020NE01084</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2659.04</v>
+        <v>5024.11</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1713,19 +1713,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°006/2018-SEINFRA - Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
+          <t>Saldo do Contrato N°011/2016-SEINFRA-Prestação de serviços para aquisição do Programa de execução de sistema de Protocolo em Plataforma WEB (sproweb) para Secretaria de Estado de Infraestrutura - SEIN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020NE01088</t>
+          <t>2020NE01089</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18765.97</v>
+        <v>45353.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1743,19 +1743,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Saldo 2º Termo Aditivo ao Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
+          <t>Saldo do 4° Termo Aditivo ao Contrato N°009/2016-SEINFRA - Prestação de Serviços de Hospedagem do Sistema Integrado° de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020NE01087</t>
+          <t>2020NE01091</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>35229.56</v>
+        <v>5797.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Saldo do Contrato N°021/2016-SEINFRA - Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
+          <t>Saldo do Contrato N°009/2016-SEINFRA - Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2015NE00986</t>
+          <t>2015NE00988</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>80/2009</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>116551.88</v>
+        <v>13519.72</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1923,14 +1923,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>T. Aditivo de Redução do Contrato nº 080/2009-SEINFRA-Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP.</t>
+          <t>Saldo do Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2015NE00993</t>
+          <t>2015NE00992</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1953,14 +1953,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11º Termo Aditivo de Redução do Contrato nº 080/2009-SEINFRA-Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP.</t>
+          <t>Anulação Total da Nota de Empenho nº 0986/2015, referente ao 11º Termo Aditivo do Contrato nº 0080/2009-SEINFRA, devido descrição da vigência incorreta.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2015NE00992</t>
+          <t>2015NE00993</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1983,19 +1983,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº 0986/2015, referente ao 11º Termo Aditivo do Contrato nº 0080/2009-SEINFRA, devido descrição da vigência incorreta.</t>
+          <t>11º Termo Aditivo de Redução do Contrato nº 080/2009-SEINFRA-Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2015NE00988</t>
+          <t>2015NE00986</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>80/2009</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13519.72</v>
+        <v>116551.88</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
+          <t>T. Aditivo de Redução do Contrato nº 080/2009-SEINFRA-Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP.</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2018NE00166</t>
+          <t>2018NE00167</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>36952.04</v>
+        <v>20186.95</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2099,28 +2099,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº. 053/2018, referente ao Contrato nº 009/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI datado de 07 d</t>
+          <t>Anulação Total da Nota de Empenho nº. 055/2018, referente ao Contrato nº 011/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI datado de 07 d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018NE00164</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21/2016</t>
-        </is>
-      </c>
+          <t>2018NE00165</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>27/02/2018</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>102740.99</v>
+        <v>2950.58</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,24 +2125,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº. 057/2018, referente ao Contrato n° 021/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI de 07 de fever</t>
+          <t>Anulação Total da Nota de Empenho nº. 0105/2018, referente ao Contrato n° 001/2017-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI de 07 de feve</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018NE00165</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>2018NE00164</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21/2016</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>27/02/2018</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2950.58</v>
+        <v>102740.99</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº. 0105/2018, referente ao Contrato n° 001/2017-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI de 07 de feve</t>
+          <t>Anulação Total da Nota de Empenho nº. 057/2018, referente ao Contrato n° 021/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI de 07 de fever</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2018NE00167</t>
+          <t>2018NE00166</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>20186.95</v>
+        <v>36952.04</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2185,14 +2185,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº. 055/2018, referente ao Contrato nº 011/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI datado de 07 d</t>
+          <t>Anulação Total da Nota de Empenho nº. 053/2018, referente ao Contrato nº 009/2016-SEINFRA, conforme ORIENTAÇÃO TÉCNICA Nº 12/2018-GISNS-SEFAZ-ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI datado de 07 d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2015NE00269</t>
+          <t>2015NE00268</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1238.23</v>
+        <v>1010.62</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D.E.A ao Cont. 030/2011-SEINFRA, referente a despesa com serviços para esta SEINFRA</t>
+          <t>D.E.A ao Cont. 030/2011 - Serviços de informática para esta SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2015NE00268</t>
+          <t>2015NE00269</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1010.62</v>
+        <v>1238.23</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>D.E.A ao Cont. 030/2011 - Serviços de informática para esta SEINFRA</t>
+          <t>D.E.A ao Cont. 030/2011-SEINFRA, referente a despesa com serviços para esta SEINFRA</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2016NE00825</t>
+          <t>2016NE00823</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>87430.28</v>
+        <v>3379.93</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2305,19 +2305,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras ¿ SICOP ao Sistema de Administração Financeira Integrada ¿ AFI ao</t>
+          <t>Saldo Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2016NE00823</t>
+          <t>2016NE00825</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3379.93</v>
+        <v>87430.28</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Saldo Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
+          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras ¿ SICOP ao Sistema de Administração Financeira Integrada ¿ AFI ao</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2023NE0000840</t>
+          <t>2023NE0000836</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2687.37</v>
+        <v>2401.81</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 0019/2019 AD: 04.</t>
+          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 019/2019 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2023NE0000836</t>
+          <t>2023NE0000840</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2401.81</v>
+        <v>2687.37</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2425,19 +2425,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 019/2019 AD: 02.</t>
+          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 0019/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2023NE0000682</t>
+          <t>2023NE0000683</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>51146.86</v>
+        <v>41829.02</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2455,19 +2455,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta SEINFRA. TC: 051/2021 AD: 01.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2023NE0000683</t>
+          <t>2023NE0000682</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>41829.02</v>
+        <v>51146.86</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2485,19 +2485,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta SEINFRA. TC: 051/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025NE0000259</t>
+          <t>2025NE0000258</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>25573.43</v>
+        <v>7121.02</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2515,19 +2515,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D.E.A. ao CT. Nº051/2021-SEINFRA, tendo como objeto: Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a p</t>
+          <t>D.E.A. referente ao CT. Nº004/2023-SEINFRA, tendo como objeto: Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus-SEINF</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025NE0000265</t>
+          <t>2025NE0000260</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2418.63</v>
+        <v>20914.51</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2545,19 +2545,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor deconteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
+          <t>D.E.A. ao CT. Nº042/2021-SEINFRA, tendo como objeto: Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a SEINFRA - Dez/2024</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025NE0000260</t>
+          <t>2025NE0000265</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>20914.51</v>
+        <v>2418.63</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2575,19 +2575,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D.E.A. ao CT. Nº042/2021-SEINFRA, tendo como objeto: Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a SEINFRA - Dez/2024</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor deconteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025NE0000258</t>
+          <t>2025NE0000259</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7121.02</v>
+        <v>25573.43</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2605,19 +2605,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>D.E.A. referente ao CT. Nº004/2023-SEINFRA, tendo como objeto: Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus-SEINF</t>
+          <t>D.E.A. ao CT. Nº051/2021-SEINFRA, tendo como objeto: Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a p</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024NE0000282</t>
+          <t>2024NE0000280</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>25573.43</v>
+        <v>20914.51</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DEA ao CT.51/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
+          <t>DEA ao CT nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a Secretaria de Infraestrutur</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2672,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024NE0000280</t>
+          <t>2024NE0000282</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>20914.51</v>
+        <v>25573.43</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DEA ao CT nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a Secretaria de Infraestrutur</t>
+          <t>DEA ao CT.51/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
         </is>
       </c>
     </row>
@@ -2728,14 +2728,10 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2022NE0000022</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>51/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000023</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>26/01/2022</t>
@@ -2751,17 +2747,21 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n° 051/2021-SEINFRA, destinados ao acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrutu</t>
+          <t>Anulação total referente ao CT. Nº051/2021-SEINFRA, em virtude da data incorreta</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2022NE0000023</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>2022NE0000022</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>51/2021</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>26/01/2022</t>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anulação total referente ao CT. Nº051/2021-SEINFRA, em virtude da data incorreta</t>
+          <t>Parte do Saldo do CT. n° 051/2021-SEINFRA, destinados ao acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrutu</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2021NE0000186</t>
+          <t>2021NE0000187</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3006.99</v>
+        <v>8807.389999999999</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. 011/2016-SEINFRA, Contratação de empresa especializada para a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do CT. 021/2016- SEINFRA, Contratação de empresa para Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infr</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2964,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2021NE0000187</t>
+          <t>2021NE0000186</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8807.389999999999</v>
+        <v>3006.99</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2987,19 +2987,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saldo do CT. 021/2016- SEINFRA, Contratação de empresa para Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infr</t>
+          <t>Parte do Saldo do CT. 011/2016-SEINFRA, Contratação de empresa especializada para a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2019NE00198</t>
+          <t>2019NE00193</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9020.969999999999</v>
+        <v>19016.02</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3017,19 +3017,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contrato nº 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do Contrato nº 009/2016-SEINFRA, destinado a Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2019NE00194</t>
+          <t>2019NE00192</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>59/2018</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12150.63</v>
+        <v>6380.01</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3047,19 +3047,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 006/2018-SEINFRA - Serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Con</t>
+          <t>Parte do Saldo do Contrato nº 059/2018-SEINFRA - Contratação de empresa para a Prestação de Serviços Técnicos em informática de forma eventual para atender da necessidade da Secretaria de Estado de In</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2019NE00196</t>
+          <t>2019NE00195</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4760.01</v>
+        <v>26422.17</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3077,19 +3077,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contrato nº 001/2017-SEINFRA. Objeto: Contratação do Serviço de licença de uso do Sistema Gestor de Conteúdo WEB para a Secretaria de Estado de Infraestrutura SEINFRA.</t>
+          <t>Parte do Saldo do CT. N°021/2016 - SEINFRA, destinados a Contratação de empresa para Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2019NE00195</t>
+          <t>2019NE00196</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>26422.17</v>
+        <v>4760.01</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3107,19 +3107,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. N°021/2016 - SEINFRA, destinados a Contratação de empresa para Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS.</t>
+          <t>Parte do Saldo do Contrato nº 001/2017-SEINFRA. Objeto: Contratação do Serviço de licença de uso do Sistema Gestor de Conteúdo WEB para a Secretaria de Estado de Infraestrutura SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2019NE00192</t>
+          <t>2019NE00194</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>59/2018</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6380.01</v>
+        <v>12150.63</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3137,19 +3137,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contrato nº 059/2018-SEINFRA - Contratação de empresa para a Prestação de Serviços Técnicos em informática de forma eventual para atender da necessidade da Secretaria de Estado de In</t>
+          <t>Saldo do Contrato nº 006/2018-SEINFRA - Serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Con</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019NE00193</t>
+          <t>2019NE00198</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19016.02</v>
+        <v>9020.969999999999</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 009/2016-SEINFRA, destinado a Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Parte do Saldo do Contrato nº 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2016NE01005</t>
+          <t>2016NE01004</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13519.72</v>
+        <v>6759.86</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2016NE01004</t>
+          <t>2016NE01005</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6759.86</v>
+        <v>13519.72</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3410,12 +3410,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2022NE0001782</t>
+          <t>2022NE0001778</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1167.84</v>
+        <v>18897.17</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3433,19 +3433,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Saldo do CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do CT. n°042/2021 - SEINFRA, prestação de serviços de hospedagem do Sistema Integrado de Controle de Obras Públicas - SICOP (e-Obras), para atender as necessidades desta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2022NE0001777</t>
+          <t>2022NE0001781</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5879.68</v>
+        <v>23550.56</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3463,19 +3463,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
+          <t>Parte do Saldo do CT. n°051/2021 - SEINFRA destinados a acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrutur</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2022NE0001781</t>
+          <t>2022NE0001777</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>23550.56</v>
+        <v>5879.68</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3493,19 +3493,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°051/2021 - SEINFRA destinados a acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrutur</t>
+          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2022NE0001778</t>
+          <t>2022NE0001782</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>18897.17</v>
+        <v>1167.84</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3523,21 +3523,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Saldo do CT. n°042/2021 - SEINFRA, prestação de serviços de hospedagem do Sistema Integrado de Controle de Obras Públicas - SICOP (e-Obras), para atender as necessidades desta SEINFRA.</t>
+          <t>Saldo do CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2019NE00856</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>19/2019</t>
-        </is>
-      </c>
+          <t>2019NE00855</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>23/09/2019</t>
@@ -3553,17 +3549,21 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Indenização para Serviços de licença de uso do sistema gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA, no período de Julho/2019, conforme NF N°9645 emitida em 25/07/20</t>
+          <t>Anulação Total da Nota de Empenho nº 823, referente RI - Reconhecimento Indenizatório nº 005/2019, destinado à Prestação de Serviços de Licença de uso de Sistemas de Informação - Gestor de conteúdo WE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2019NE00855</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>2019NE00856</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>19/2019</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>23/09/2019</t>
@@ -3579,14 +3579,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Anulação Total da Nota de Empenho nº 823, referente RI - Reconhecimento Indenizatório nº 005/2019, destinado à Prestação de Serviços de Licença de uso de Sistemas de Informação - Gestor de conteúdo WE</t>
+          <t>Indenização para Serviços de licença de uso do sistema gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA, no período de Julho/2019, conforme NF N°9645 emitida em 25/07/20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2016NE00810</t>
+          <t>2016NE00816</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5767.7</v>
+        <v>11535.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2016NE00816</t>
+          <t>2016NE00810</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11535.4</v>
+        <v>5767.7</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3702,12 +3702,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024NE0000088</t>
+          <t>2024NE0000091</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7121.02</v>
+        <v>1034.2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3725,14 +3725,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>D.E.A ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Estado de Infraestrutura – SEINFRA. - Período: Novembro/2023 - N</t>
+          <t>D.E.A. ao Contrato nº 041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades da S</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024NE0000077</t>
+          <t>2024NE0000073</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5967.13</v>
+        <v>3487.43</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3755,19 +3755,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DEA ao CT.51/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
+          <t>DEA ao CT.051/2021-SEINFRA, destinados Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infraes</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024NE0000099</t>
+          <t>2024NE0000085</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2687.37</v>
+        <v>7121.02</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3785,19 +3785,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. n°019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perío</t>
+          <t>D.E.A ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. - Per</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024NE0000095</t>
+          <t>2024NE0000082</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2687.37</v>
+        <v>7121.02</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3815,19 +3815,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. n°019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perío</t>
+          <t>PROC.025101.5856/2023-11 - Referente ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropoli</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024NE0000098</t>
+          <t>2024NE0000069</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2687.37</v>
+        <v>20914.51</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. nº 019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perí</t>
+          <t>DEA ao Contrato nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão deObras-E-Obras para a Secretaria de Infraest</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024NE0000072</t>
+          <t>2024NE0000075</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>25573.43</v>
+        <v>19606.3</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3875,14 +3875,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>DEA ao CT n°051/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs,para esta Secretaria de Estado de Infr</t>
+          <t>DEA ao CT.051/2021-SEINFRA destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024NE0000075</t>
+          <t>2024NE0000072</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>19606.3</v>
+        <v>25573.43</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3905,19 +3905,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>DEA ao CT.051/2021-SEINFRA destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
+          <t>DEA ao CT n°051/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs,para esta Secretaria de Estado de Infr</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024NE0000069</t>
+          <t>2024NE0000098</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>20914.51</v>
+        <v>2687.37</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3935,19 +3935,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>DEA ao Contrato nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão deObras-E-Obras para a Secretaria de Infraest</t>
+          <t>D.E.A ao CT. nº 019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perí</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2024NE0000082</t>
+          <t>2024NE0000095</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7121.02</v>
+        <v>2687.37</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3965,19 +3965,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PROC.025101.5856/2023-11 - Referente ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropoli</t>
+          <t>D.E.A ao CT. n°019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perío</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024NE0000085</t>
+          <t>2024NE0000099</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7121.02</v>
+        <v>2687.37</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>D.E.A ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. - Per</t>
+          <t>D.E.A ao CT. n°019/2019-SEINFRA, referente a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura-SEINFRA. Perío</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024NE0000073</t>
+          <t>2024NE0000077</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3487.43</v>
+        <v>5967.13</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4025,19 +4025,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DEA ao CT.051/2021-SEINFRA, destinados Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infraes</t>
+          <t>DEA ao CT.51/2021-SEINFRA, destinados a Serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta Secretaria de Estado de Infrae</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024NE0000091</t>
+          <t>2024NE0000088</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1034.2</v>
+        <v>7121.02</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>D.E.A. ao Contrato nº 041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades da S</t>
+          <t>D.E.A ao Contrato nº 004/2023-SEINFRA, destinados a Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Estado de Infraestrutura – SEINFRA. - Período: Novembro/2023 - N</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4152,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024NE0001550</t>
+          <t>2024NE0001552</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>14242.04</v>
+        <v>36948.96</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
@@ -4212,12 +4212,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024NE0001552</t>
+          <t>2024NE0001550</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>36948.96</v>
+        <v>14242.04</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4235,14 +4235,14 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020NE01013</t>
+          <t>2020NE01012</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7933.35</v>
+        <v>45353.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4261,14 +4261,14 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anulação total da NE N°749/2020, referente ao CT. N°019/2019 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação parcial da NE N°510/2020, referente ao CT. N°009/2016 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020NE00998</t>
+          <t>2020NE01005</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5797.1</v>
+        <v>18765.97</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°004/2020, referente ao CT. N°009/2016 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação parcial da NE N°326/2020, referente ao CT. N°006/2018 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020NE01001</t>
+          <t>2020NE01003</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2659.04</v>
+        <v>35229.56</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°006/2020, referente ao CT. N°006/2018 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação parcial da NE N°018/2020, referente ao CT. N°021/2016 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020NE01003</t>
+          <t>2020NE01001</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>35229.56</v>
+        <v>2659.04</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4365,14 +4365,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°018/2020, referente ao CT. N°021/2016 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação parcial da NE N°006/2020, referente ao CT. N°006/2018 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020NE01005</t>
+          <t>2020NE00998</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>18765.97</v>
+        <v>5797.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4391,14 +4391,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°326/2020, referente ao CT. N°006/2018 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação parcial da NE N°004/2020, referente ao CT. N°009/2016 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020NE01012</t>
+          <t>2020NE01013</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>45353.4</v>
+        <v>7933.35</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE N°510/2020, referente ao CT. N°009/2016 - SEINFRA, em virtude de troca de fonte.</t>
+          <t>Anulação total da NE N°749/2020, referente ao CT. N°019/2019 - SEINFRA, em virtude de troca de fonte.</t>
         </is>
       </c>
     </row>
@@ -4454,21 +4454,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2017NE00486</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2017NE00485</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>22/05/2017</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7198.43</v>
+        <v>10287.63</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4477,24 +4473,28 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1° Termo Aditivo ao Contrato nº 009/2016-SEINFRA, tendo como objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP.</t>
+          <t>Anulação Total da NE n° 303/2017 em virtude de ter sido empenhado a maior.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2017NE00485</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>2017NE00486</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
           <t>22/05/2017</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10287.63</v>
+        <v>7198.43</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anulação Total da NE n° 303/2017 em virtude de ter sido empenhado a maior.</t>
+          <t>1° Termo Aditivo ao Contrato nº 009/2016-SEINFRA, tendo como objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2022NE0002011</t>
+          <t>2022NE0002009</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2401.81</v>
+        <v>5879.68</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT.019/2019-SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -4750,12 +4750,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2022NE0002009</t>
+          <t>2022NE0002011</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5879.68</v>
+        <v>2401.81</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4773,19 +4773,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamentos de Segurança para a Rede interna desta SEINFRA.</t>
+          <t>Parte do Saldo do CT.019/2019-SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021NE0001358</t>
+          <t>2021NE0001357</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6284.16</v>
+        <v>23639.75</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contrato nº 019/2019-SEINFRA, tendo como objeto: Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraes</t>
+          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados a Contratação de empresa para Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS para a SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2021NE0001357</t>
+          <t>2021NE0001358</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>23639.75</v>
+        <v>6284.16</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados a Contratação de empresa para Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS para a SEINFRA.</t>
+          <t>Parte do Saldo do Contrato nº 019/2019-SEINFRA, tendo como objeto: Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraes</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2020NE00245</t>
+          <t>2020NE00242</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados a Licença de uso de sistema de informação Sistema Gestor de Conteudo Web, referente a Dezembro/2019.</t>
+          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados à Licença de uso de sistema de informação Sistema Gestor de Conteudo Web., referente ao mês de Outubro/2019.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020NE00251</t>
+          <t>2020NE00238</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1586.67</v>
+        <v>1080.71</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados à Licença de uso de sistema de informação Sistema Gestor de Conteudo Web., referente ao mês de Novembro/2019.</t>
+          <t>D.E.A ao CT. N°007/2015 -SRMM, destinados aos Serviços de Sistema de Sproweb, referente ao mês de Novembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020NE00255</t>
+          <t>2020NE00236</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>653.91</v>
+        <v>1025.51</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5023,14 +5023,14 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°009/2016 - SEINFRA, destinados ao Serviço de Hospedagem de Sistemas, referente ao mês de Dezembro/2019.</t>
+          <t>D.E.A ao CT. N°007/2015 - SRMM, destinados à Sistema de Sproweb, referente ao mês de Setembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020NE00257</t>
+          <t>2020NE00233</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8376.48</v>
+        <v>1106.93</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5049,14 +5049,14 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Dezembro/2019.</t>
+          <t>D.E.A ao CT. N°007/2015 - SRMM, destinados à Sistema de Sproweb, referente ao mês de Dezembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020NE00258</t>
+          <t>2020NE00260</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5075,14 +5075,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Outubro/2019.</t>
+          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Novembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020NE00260</t>
+          <t>2020NE00258</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Novembro/2019.</t>
+          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Outubro/2019.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020NE00233</t>
+          <t>2020NE00257</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1106.93</v>
+        <v>8376.48</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5127,14 +5127,14 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°007/2015 - SRMM, destinados à Sistema de Sproweb, referente ao mês de Dezembro/2019.</t>
+          <t>D.E.A ao CT. N°002/2016 - SRMM, destinados à Serviço de Acesso à Rede Mundial de Computadores, referente ao mês de Dezembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2020NE00236</t>
+          <t>2020NE00255</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1025.51</v>
+        <v>653.91</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°007/2015 - SRMM, destinados à Sistema de Sproweb, referente ao mês de Setembro/2019.</t>
+          <t>D.E.A ao CT. N°009/2016 - SEINFRA, destinados ao Serviço de Hospedagem de Sistemas, referente ao mês de Dezembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2020NE00238</t>
+          <t>2020NE00251</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1080.71</v>
+        <v>1586.67</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5179,14 +5179,14 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°007/2015 -SRMM, destinados aos Serviços de Sistema de Sproweb, referente ao mês de Novembro/2019.</t>
+          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados à Licença de uso de sistema de informação Sistema Gestor de Conteudo Web., referente ao mês de Novembro/2019.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020NE00242</t>
+          <t>2020NE00245</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados à Licença de uso de sistema de informação Sistema Gestor de Conteudo Web., referente ao mês de Outubro/2019.</t>
+          <t>D.E.A ao CT. N°004/2017 - SRMM, destinados a Licença de uso de sistema de informação Sistema Gestor de Conteudo Web, referente a Dezembro/2019.</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2023NE0000136</t>
+          <t>2023NE0000080</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4705.93</v>
+        <v>2401.81</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5527,19 +5527,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>PROC.025101.007220/2022-23 - Referente ao Contrato nº 006/2018-SEINFRA, destinados Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA - Periodo: Dezembro/2</t>
+          <t>PROC.025101.007221/2022-78 - Referente ao Contrato nº 019/2019-SEINFRA, destinados a Prestacao de Servicos de Uso de Sistema de Gestao de Conteudo Web - Periodo: Dezembro/2022 - Nfs.: 33996 Emissao: 0</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2023NE0000080</t>
+          <t>2023NE0000136</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2401.81</v>
+        <v>4705.93</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5557,19 +5557,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PROC.025101.007221/2022-78 - Referente ao Contrato nº 019/2019-SEINFRA, destinados a Prestacao de Servicos de Uso de Sistema de Gestao de Conteudo Web - Periodo: Dezembro/2022 - Nfs.: 33996 Emissao: 0</t>
+          <t>PROC.025101.007220/2022-23 - Referente ao Contrato nº 006/2018-SEINFRA, destinados Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA - Periodo: Dezembro/2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2020NE00972</t>
+          <t>2020NE00978</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>8807.389999999999</v>
+        <v>10216.16</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5587,19 +5587,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
+          <t>Termo aditivo ao Contrato N° 009/2016- SEINFRA, Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020NE00978</t>
+          <t>2020NE00972</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10216.16</v>
+        <v>8807.389999999999</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Termo aditivo ao Contrato N° 009/2016- SEINFRA, Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2023NE0000004</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>13915.25</v>
+        <v>9607.24</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5703,19 +5703,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Anulação total da NE n°001/2023, referente ao CT. n°006/2018 - SEINFRA, em virtude do ajuste na data de emissão.</t>
+          <t>Anulação total da NE n°002/2023, referente ao CT. n°019/2019 - SEINFRA, em virtude do ajuste na data de emissão.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2023NE0000001</t>
+          <t>2023NE0000002</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>13915.25</v>
+        <v>9607.24</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5733,19 +5733,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 006/2018-SEINFRA, tendo como objeto: Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA (Serviços de Firewall, compreendendo os Serviç</t>
+          <t>Parte do Saldo do CT. n°019/2019 - SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2023NE0000002</t>
+          <t>2023NE0000001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>9607.24</v>
+        <v>13915.25</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°019/2019 - SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Saldo do Contrato nº 006/2018-SEINFRA, tendo como objeto: Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA (Serviços de Firewall, compreendendo os Serviç</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000004</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>9607.24</v>
+        <v>13915.25</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Anulação total da NE n°002/2023, referente ao CT. n°019/2019 - SEINFRA, em virtude do ajuste na data de emissão.</t>
+          <t>Anulação total da NE n°001/2023, referente ao CT. n°006/2018 - SEINFRA, em virtude do ajuste na data de emissão.</t>
         </is>
       </c>
     </row>
@@ -5886,12 +5886,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
+          <t>2026NE0000003</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11222.2</v>
+        <v>26335.47</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5909,19 +5909,19 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA. TC: 0011/2024 AD: 01</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
+          <t>2026NE0000004</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>26335.47</v>
+        <v>11222.2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA. TC: 0011/2024 AD: 01</t>
         </is>
       </c>
     </row>
@@ -6036,12 +6036,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021NE0000072</t>
+          <t>2021NE0000073</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2734.15</v>
+        <v>1475.29</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6059,19 +6059,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 011/2016-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB)</t>
+          <t>D.E.A ao CT. 01/2017-SEINFRA, destinados a Contratação do Serviço de licença de uso do Sistema Gestor de Conteúdo WEB para a Secretaria de Estado de Infraestrutura-SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021NE0000074</t>
+          <t>2021NE0000075</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3794.11</v>
+        <v>8440.530000000001</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6089,24 +6089,28 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
+          <t>D.E.A ao CT. 021/2016-SEINFRA, destinados ao Acesso a Internet com link dedicado 06 (seis) MBPS e circuito de transmissão de dados pontos de 10 MBPS</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021NE0000070</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr"/>
+          <t>2021NE0000071</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C190" t="inlineStr">
         <is>
           <t>15/02/2021</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>34965.64</v>
+        <v>9508.01</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6115,28 +6119,24 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 080/2009, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas.</t>
+          <t>D.E.A ao CT. 09/2016-SEINFRA, destinados a Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrada AF</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021NE0000071</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000070</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>15/02/2021</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>9508.01</v>
+        <v>34965.64</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6145,19 +6145,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 09/2016-SEINFRA, destinados a Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrada AF</t>
+          <t>D.E.A ao CT. 080/2009, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021NE0000075</t>
+          <t>2021NE0000074</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>8440.530000000001</v>
+        <v>3794.11</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6175,19 +6175,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 021/2016-SEINFRA, destinados ao Acesso a Internet com link dedicado 06 (seis) MBPS e circuito de transmissão de dados pontos de 10 MBPS</t>
+          <t>D.E.A ao CT. 006/2018-SEINFRA, destinados a Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021NE0000073</t>
+          <t>2021NE0000072</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1475.29</v>
+        <v>2734.15</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. 01/2017-SEINFRA, destinados a Contratação do Serviço de licença de uso do Sistema Gestor de Conteúdo WEB para a Secretaria de Estado de Infraestrutura-SEINFRA</t>
+          <t>D.E.A ao CT. 011/2016-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB)</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025NE0000348</t>
+          <t>2025NE0000337</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>51146.86</v>
+        <v>7121.02</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6339,19 +6339,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025NE0000344</t>
+          <t>2025NE0000339</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>25794.57</v>
+        <v>5374.74</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6369,19 +6369,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025NE0000339</t>
+          <t>2025NE0000344</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5374.74</v>
+        <v>25794.57</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6399,19 +6399,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025NE0000337</t>
+          <t>2025NE0000348</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7121.02</v>
+        <v>51146.86</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6429,19 +6429,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2017NE01185</t>
+          <t>2017NE01184</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2883.85</v>
+        <v>10327.03</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do CT. nº 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6496,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2017NE01184</t>
+          <t>2017NE01185</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>10327.03</v>
+        <v>2883.85</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6519,19 +6519,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Saldo do CT. nº 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo Web.</t>
+          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025NE0001046</t>
+          <t>2025NE0001045</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>19606.28</v>
+        <v>14767.58</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6549,19 +6549,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025NE0001045</t>
+          <t>2025NE0001046</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>14767.58</v>
+        <v>19606.28</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6579,28 +6579,24 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021NE0001608</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>51/2021</t>
-        </is>
-      </c>
+          <t>2021NE0001610</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
           <t>12/11/2021</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>17107.14</v>
+        <v>11153.54</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6616,17 +6612,21 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021NE0001610</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
+          <t>2021NE0001608</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>51/2021</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
           <t>12/11/2021</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>11153.54</v>
+        <v>17107.14</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6672,10 +6672,14 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2017NE00314</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
+          <t>2017NE00315</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>61/2012</t>
+        </is>
+      </c>
       <c r="C210" t="inlineStr">
         <is>
           <t>12/04/2017</t>
@@ -6691,21 +6695,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Anulação total da NE N° 304/2017, referente ao Contrato n° 061/2012-SEINFRA em virtude de Referência incorreta.</t>
+          <t>Saldo do Contrato nº 061/2012-SEINFRA, tendo como objeto: Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manaus/AM</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2017NE00315</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>61/2012</t>
-        </is>
-      </c>
+          <t>2017NE00314</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
           <t>12/04/2017</t>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 061/2012-SEINFRA, tendo como objeto: Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manaus/AM</t>
+          <t>Anulação total da NE N° 304/2017, referente ao Contrato n° 061/2012-SEINFRA em virtude de Referência incorreta.</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021NE0000947</t>
+          <t>2021NE0000943</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>13381.06</v>
+        <v>2094.72</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. Nº021-2016-SEINFRA, destinados ao Acesso a Internet com Link dedicado 100 (cem) MBPS e Circuito de Transmissão de Dados pontos de 100 MBPS para a Secretaria de Estado de Infraest</t>
+          <t xml:space="preserve">Parte do Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - </t>
         </is>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021NE0000943</t>
+          <t>2021NE0000947</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2094.72</v>
+        <v>13381.06</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6957,19 +6957,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - </t>
+          <t>Parte do Saldo do CT. Nº021-2016-SEINFRA, destinados ao Acesso a Internet com Link dedicado 100 (cem) MBPS e Circuito de Transmissão de Dados pontos de 100 MBPS para a Secretaria de Estado de Infraest</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2024NE0000994</t>
+          <t>2024NE0000972</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>14242.04</v>
+        <v>41829.02</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6987,19 +6987,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2024NE0000986</t>
+          <t>2024NE0000971</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>51146.86</v>
+        <v>2687.37</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7017,19 +7017,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 0019/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2024NE0000971</t>
+          <t>2024NE0000986</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2687.37</v>
+        <v>51146.86</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7047,19 +7047,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA. TC: 0019/2019 AD: 04.</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2024NE0000972</t>
+          <t>2024NE0000994</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>41829.02</v>
+        <v>14242.04</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025NE0001167</t>
+          <t>2025NE0001171</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>51146.86</v>
+        <v>5374.74</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7463,19 +7463,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025NE0001171</t>
+          <t>2025NE0001167</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>5374.74</v>
+        <v>51146.86</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021NE0000251</t>
+          <t>2021NE0000250</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>6013.98</v>
+        <v>17614.78</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7553,19 +7553,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. 011/2016- SEINFRA, Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Parte do Saldo do CT. 021/2016 - SEINFRA, Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infraestrutura e Regiã</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021NE0000253</t>
+          <t>2021NE0000252</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>9974.860000000001</v>
+        <v>4760.01</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7583,19 +7583,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. 006/2018-SEINFRA, Contratação de empresa para Prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus - SEINFRA.</t>
+          <t>Parte do Saldo do CT. 019/2019-SEINFRA, Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021NE0000252</t>
+          <t>2021NE0000253</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>4760.01</v>
+        <v>9974.860000000001</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7613,19 +7613,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. 019/2019-SEINFRA, Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. 006/2018-SEINFRA, Contratação de empresa para Prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021NE0000250</t>
+          <t>2021NE0000251</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>17614.78</v>
+        <v>6013.98</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. 021/2016 - SEINFRA, Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infraestrutura e Regiã</t>
+          <t>Parte do Saldo do CT. 011/2016- SEINFRA, Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -7680,10 +7680,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2024NE0001433</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>2024NE0001432</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>42/2021</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>07/10/2024</t>
@@ -7699,7 +7703,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Anulação total da NE n°1432/2024, em virtude de ajuste no cronograma.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
@@ -7732,14 +7736,10 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2024NE0001432</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>42/2021</t>
-        </is>
-      </c>
+          <t>2024NE0001433</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
           <t>07/10/2024</t>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Anulação total da NE n°1432/2024, em virtude de ajuste no cronograma.</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2018NE00801</t>
+          <t>2018NE00800</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>14419.25</v>
+        <v>2179.35</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7815,19 +7815,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo Contrato nº 011/2016-SEINFRA - Prest. de serviços para aquisição do (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos para SEINFRA</t>
+          <t>D.E.A ao CT. N°021/2016 - Prestação de Serviços de Gerenciamento de rede no mes de Dezembro/2016.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2018NE00800</t>
+          <t>2018NE00801</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2179.35</v>
+        <v>14419.25</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°021/2016 - Prestação de Serviços de Gerenciamento de rede no mes de Dezembro/2016.</t>
+          <t>1º Termo Aditivo Contrato nº 011/2016-SEINFRA - Prest. de serviços para aquisição do (SPROWEB), objetivando o controle e acompanhamento do registro de todos os documentos ou processos para SEINFRA</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2015NE00595</t>
+          <t>2015NE00591</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Anulação total da NE N°591/2015, referente ao CT. N° 029/2014, em virtude do ítem Referência incorreto.</t>
+          <t>2º Termo Aditivo ao Contrato nº 029/2014 - SEINFRA - Serviço de Utilização de Protocolo em Plataforma WEB para Uso Exclusivo desta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2015NE00596</t>
+          <t>2015NE00584</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>NE 596 DE 07/05/2015 R$ 23.391,00 MAIO - R$ 5.198,00 JUNHO Á DEZEMBRO - 2.599,00 2º Termo Aditivo ao Contrato 029/2014 Reajuste de 3,96%</t>
+          <t>Anulação total da Nota de Empenho nº 574/2015, descrição incorreta.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2015NE00584</t>
+          <t>2015NE00596</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Anulação total da Nota de Empenho nº 574/2015, descrição incorreta.</t>
+          <t>NE 596 DE 07/05/2015 R$ 23.391,00 MAIO - R$ 5.198,00 JUNHO Á DEZEMBRO - 2.599,00 2º Termo Aditivo ao Contrato 029/2014 Reajuste de 3,96%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2015NE00591</t>
+          <t>2015NE00595</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8025,19 +8025,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contrato nº 029/2014 - SEINFRA - Serviço de Utilização de Protocolo em Plataforma WEB para Uso Exclusivo desta SEINFRA.</t>
+          <t>Anulação total da NE N°591/2015, referente ao CT. N° 029/2014, em virtude do ítem Referência incorreto.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2024NE0000410</t>
+          <t>2024NE0000413</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>41829.02</v>
+        <v>51146.86</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8055,19 +8055,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2024NE0000413</t>
+          <t>2024NE0000410</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>51146.86</v>
+        <v>41829.02</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8085,19 +8085,19 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2022NE0000067</t>
+          <t>2022NE0000065</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>P.286/2021</t>
+          <t>P.323/2021</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>818.66</v>
+        <v>821.7</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8115,19 +8115,19 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 63, GRUPO 459 - SEM CONTRATO - MÊS DE AGOSTO/2021. PARECER JURÍDICO Nº 1149/2021-AJUR.</t>
+          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 68, GRUPO 459 - SEM CONTRATO - MÊS DE JULHO/2021. PARECER JURÍDICO Nº 1150/2021-AJUR.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2022NE0000068</t>
+          <t>2022NE0000069</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>P.254/2021</t>
+          <t>P.198/2021</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 65, GRUPO 459 - SEM CONTRATO - MÊS DE JULHO/2021. PARECER JURÍDICO Nº 1145/2021-AJUR.</t>
+          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 63, GRUPO 459 - SEM CONTRATO - MÊS DE MAIO/2021. PARECER JURÍDICO Nº 01087/2021-AJUR.</t>
         </is>
       </c>
     </row>
@@ -8182,12 +8182,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2022NE0000069</t>
+          <t>2022NE0000068</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>P.198/2021</t>
+          <t>P.254/2021</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8205,19 +8205,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 63, GRUPO 459 - SEM CONTRATO - MÊS DE MAIO/2021. PARECER JURÍDICO Nº 01087/2021-AJUR.</t>
+          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 65, GRUPO 459 - SEM CONTRATO - MÊS DE JULHO/2021. PARECER JURÍDICO Nº 1145/2021-AJUR.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2022NE0000065</t>
+          <t>2022NE0000067</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>P.323/2021</t>
+          <t>P.286/2021</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>821.7</v>
+        <v>818.66</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 68, GRUPO 459 - SEM CONTRATO - MÊS DE JULHO/2021. PARECER JURÍDICO Nº 1150/2021-AJUR.</t>
+          <t>EXECUÇÃO DE SISTEMAS SISTEMA: SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO ESPECIAL TIPO 63, GRUPO 459 - SEM CONTRATO - MÊS DE AGOSTO/2021. PARECER JURÍDICO Nº 1149/2021-AJUR.</t>
         </is>
       </c>
     </row>
@@ -8272,12 +8272,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2023NE0001303</t>
+          <t>2023NE0001301</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>16034.45</v>
+        <v>969.6</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta SEINFRA. TC: 041/2021 A</t>
         </is>
       </c>
     </row>
@@ -8332,12 +8332,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2023NE0001301</t>
+          <t>2023NE0001303</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>969.6</v>
+        <v>16034.45</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8355,19 +8355,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta SEINFRA. TC: 041/2021 A</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2017NE00304</t>
+          <t>2017NE00312</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>10139.79</v>
+        <v>11535.4</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8385,19 +8385,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manaus/AM</t>
+          <t>Saldo do CT. N°011/2016 - Aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2017NE00305</t>
+          <t>2017NE00303</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>37360.36</v>
+        <v>10287.63</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8415,19 +8415,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 021/2016-SEINFRA, tendo como objeto: Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, Parecer Jurídico nº 0625/2016-AJUR.</t>
+          <t>Saldo do Contrato nº 009/2016-SEINFRA. Objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrad</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2017NE00303</t>
+          <t>2017NE00305</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>10287.63</v>
+        <v>37360.36</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8445,19 +8445,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 009/2016-SEINFRA. Objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrad</t>
+          <t>Saldo do Contrato nº 021/2016-SEINFRA, tendo como objeto: Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, Parecer Jurídico nº 0625/2016-AJUR.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2017NE00312</t>
+          <t>2017NE00304</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>11535.4</v>
+        <v>10139.79</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8475,24 +8475,28 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°011/2016 - Aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do Contrato nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manaus/AM</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2020NE00328</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
+          <t>2020NE00326</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>6/2018</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
           <t>06/03/2020</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1080.05</v>
+        <v>39017.02</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8501,28 +8505,24 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Anulação Parcial da Nota de Empenho nº 006/2020, referente ao Contrato nº 006/2018-SEINFRA, em virtude do encerramento da vigência contratual em 12/03/2020.</t>
+          <t>2º Termo Aditivo ao Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2020NE00326</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>6/2018</t>
-        </is>
-      </c>
+          <t>2020NE00328</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
           <t>06/03/2020</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>39017.02</v>
+        <v>1080.05</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8531,19 +8531,19 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
+          <t>Anulação Parcial da Nota de Empenho nº 006/2020, referente ao Contrato nº 006/2018-SEINFRA, em virtude do encerramento da vigência contratual em 12/03/2020.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2022NE0001886</t>
+          <t>2022NE0001885</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>16034.45</v>
+        <v>1034.2</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8561,19 +8561,19 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Termo Aditivo ao CT.042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a Secretaria de Infrae</t>
+          <t xml:space="preserve">Termo Aditivo ao CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta </t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2022NE0001885</t>
+          <t>2022NE0001886</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1034.2</v>
+        <v>16034.45</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8591,19 +8591,19 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo Aditivo ao CT.041/2021-SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades desta </t>
+          <t>Termo Aditivo ao CT.042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras-E-Obras para a Secretaria de Infrae</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2024NE0000774</t>
+          <t>2024NE0000773</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>51146.86</v>
+        <v>41829.02</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2024NE0000773</t>
+          <t>2024NE0000774</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>41829.02</v>
+        <v>51146.86</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8681,19 +8681,19 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2022NE0000788</t>
+          <t>2022NE0000791</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>6284.16</v>
+        <v>75588.67999999999</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8711,19 +8711,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. n°042/2021 - SEINFRA, destinados a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP (e-Obras) , para atender as necessidades da SEIN</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2022NE0000790</t>
+          <t>2022NE0000787</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>4671.36</v>
+        <v>23518.72</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8741,19 +8741,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do CT. n°041/2021 - SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades </t>
+          <t xml:space="preserve">Parte do Saldo do Contrato nº 006/2018-SEINFRA, tendo como objeto: Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA (Serviços de Firewall, compreendendo </t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2022NE0000787</t>
+          <t>2022NE0000790</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>23518.72</v>
+        <v>4671.36</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8771,19 +8771,19 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do Contrato nº 006/2018-SEINFRA, tendo como objeto: Prestação de Serviços de locação de equipamentos de segurança para a rede interna desta SEINFRA (Serviços de Firewall, compreendendo </t>
+          <t xml:space="preserve">Parte do Saldo do CT. n°041/2021 - SEINFRA, destinados a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades </t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2022NE0000791</t>
+          <t>2022NE0000788</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>75588.67999999999</v>
+        <v>6284.16</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°042/2021 - SEINFRA, destinados a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP (e-Obras) , para atender as necessidades da SEIN</t>
+          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2015NE00035</t>
+          <t>2015NE00042</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8891,19 +8891,19 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 080/2009-SEINFRA, tendo como objeto: Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas., conforme Parecer Jurídico nº 1358/2013</t>
+          <t>Cobertura financeira 2015: janeiro a março</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2015NE00072</t>
+          <t>2015NE00033</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>30/2011</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>5193.6</v>
+        <v>10139.79</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8928,12 +8928,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2015NE00063</t>
+          <t>2015NE00094</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>29/2014</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>3379.93</v>
+        <v>2051.4</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2015NE00046</t>
+          <t>2015NE00093</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7500</v>
+        <v>2516.25</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8981,14 +8981,14 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Cancelamento da NE 0038/2015, em função de descrição incompleta.</t>
+          <t>Reconhecimento de dívida do exercício de 2014</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2015NE00031</t>
+          <t>2015NE00071</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9011,14 +9011,14 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 030/2011 - Serviços de Informática de Forma Eventual para SEINFRA.</t>
+          <t>Anulação total da NE 031/15, em função de descrição incompleta.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2015NE00048</t>
+          <t>2015NE00038</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015: janeiro a março</t>
+          <t>Contrato nº029/2014-SEINFRA - Prestação de Serv. do Sistema SPROWEB desta SEINFRA/AM</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2015NE00038</t>
+          <t>2015NE00048</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9101,14 +9101,14 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Contrato nº029/2014-SEINFRA - Prestação de Serv. do Sistema SPROWEB desta SEINFRA/AM</t>
+          <t>Cobertura financeira 2015: janeiro a março</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2015NE00071</t>
+          <t>2015NE00031</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9131,14 +9131,14 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Anulação total da NE 031/15, em função de descrição incompleta.</t>
+          <t>Saldo do Contrato nº 030/2011 - Serviços de Informática de Forma Eventual para SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2015NE00093</t>
+          <t>2015NE00046</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>2516.25</v>
+        <v>7500</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9161,19 +9161,19 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida do exercício de 2014</t>
+          <t>Cancelamento da NE 0038/2015, em função de descrição incompleta.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2015NE00094</t>
+          <t>2015NE00063</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>29/2014</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>2051.4</v>
+        <v>3379.93</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9198,12 +9198,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2015NE00033</t>
+          <t>2015NE00072</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>30/2011</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>10139.79</v>
+        <v>5193.6</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2015NE00042</t>
+          <t>2015NE00035</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015: janeiro a março</t>
+          <t>Saldo do Contrato nº 080/2009-SEINFRA, tendo como objeto: Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas., conforme Parecer Jurídico nº 1358/2013</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2024NE0000394</t>
+          <t>2024NE0000392</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>7121.02</v>
+        <v>10733.42</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>DEA ao CT nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão deObras-E-Obras para a Secretaria de Infraestrutura</t>
         </is>
       </c>
     </row>
@@ -9438,12 +9438,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2024NE0000392</t>
+          <t>2024NE0000394</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>10733.42</v>
+        <v>7121.02</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9461,28 +9461,24 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DEA ao CT nº 042/2021-SEINFRA, destinados a Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão deObras-E-Obras para a Secretaria de Infraestrutura</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2021NE0000006</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>21/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000027</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>26422.17</v>
+        <v>38292.42</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9491,19 +9487,19 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Saldo do CT. 021/2016-SEINFRA, Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infraestrutura e Região Metropoli</t>
+          <t>Anulação Total da NE N. 002/2021, referente ao CT. 009/2016 - SEINFRA, em virtude de alteração no Cronograma.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2021NE0000021</t>
+          <t>2021NE0000005</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9512,7 +9508,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>8100.42</v>
+        <v>9020.969999999999</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9521,19 +9517,19 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
+          <t xml:space="preserve">Parte do Saldo do CT. 011/2016-SEINFRA, destinados a Contratação de empresa especializada para a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB </t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2021NE0000023</t>
+          <t>2021NE0000002</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9542,7 +9538,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4760.01</v>
+        <v>38292.42</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9551,24 +9547,28 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Parte do Saldo do Contrato n° 019/2019-SEINFRA, Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Saldo do CT. N° 009/2016-SEINFRA -Contratação de empresa para Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2021NE0000028</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>2021NE0000032</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>8100.42</v>
+        <v>38352.42</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Anulação Total da NE N. 021/2021, referente ao CT. 006/2018 - SEINFRA, em virtude de alteração no Cronograma.</t>
+          <t>Parte do Saldo do CT. N°009/2016 - SEINFRA, destinados a Contratação de empresa para serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras – SICOP.</t>
         </is>
       </c>
     </row>
@@ -9614,21 +9614,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2021NE0000032</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000028</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>38352.42</v>
+        <v>8100.42</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9637,19 +9633,19 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. N°009/2016 - SEINFRA, destinados a Contratação de empresa para serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras – SICOP.</t>
+          <t>Anulação Total da NE N. 021/2021, referente ao CT. 006/2018 - SEINFRA, em virtude de alteração no Cronograma.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2021NE0000002</t>
+          <t>2021NE0000023</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9658,7 +9654,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>38292.42</v>
+        <v>4760.01</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -9667,19 +9663,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Saldo do CT. N° 009/2016-SEINFRA -Contratação de empresa para Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Parte do Saldo do Contrato n° 019/2019-SEINFRA, Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2021NE0000005</t>
+          <t>2021NE0000021</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9688,7 +9684,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>9020.969999999999</v>
+        <v>8100.42</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -9697,24 +9693,28 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do CT. 011/2016-SEINFRA, destinados a Contratação de empresa especializada para a Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB </t>
+          <t>Parte do Saldo do Contato Nº 006/2018-SEINFRA - Prestação de Serviços de Locação de Equipamento de Segurança para a Rede Interna desta Secretaria de Estado de Infraestrutura SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2021NE0000027</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
+          <t>2021NE0000006</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>21/2016</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>38292.42</v>
+        <v>26422.17</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9723,19 +9723,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Anulação Total da NE N. 002/2021, referente ao CT. 009/2016 - SEINFRA, em virtude de alteração no Cronograma.</t>
+          <t>Saldo do CT. 021/2016-SEINFRA, Acesso à Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS, para a Secretaria de Estado de Infraestrutura e Região Metropoli</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2016NE00053</t>
+          <t>2016NE00057</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>29/2014</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>10396</v>
+        <v>20279.58</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9753,19 +9753,19 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de utilização de sistema Protocolo em Plataforma Wel para Controle e acompanhamento de Documentos Registrados em meio Virtual para uso exclusivo da SEINFRA.</t>
+          <t>Saldo Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2016NE00057</t>
+          <t>2016NE00053</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>29/2014</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>20279.58</v>
+        <v>10396</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9783,19 +9783,19 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Saldo Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
+          <t>Contratação de Prestação de Serviços de utilização de sistema Protocolo em Plataforma Wel para Controle e acompanhamento de Documentos Registrados em meio Virtual para uso exclusivo da SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025NE0001451</t>
+          <t>2025NE0001462</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>5330.55</v>
+        <v>31812.55</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9813,19 +9813,19 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA. TC: 0011/2024 AD: 01</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025NE0001462</t>
+          <t>2025NE0001451</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>31812.55</v>
+        <v>5330.55</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9843,19 +9843,19 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA. TC: 0011/2024 AD: 01</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024NE0001304</t>
+          <t>2024NE0001306</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>7121.02</v>
+        <v>25794.57</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9873,19 +9873,19 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024NE0001306</t>
+          <t>2024NE0001304</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>25794.57</v>
+        <v>7121.02</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2025NE0000858</t>
+          <t>2025NE0000861</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>4880.06</v>
+        <v>14767.58</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -9996,12 +9996,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2025NE0000861</t>
+          <t>2025NE0000858</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>14767.58</v>
+        <v>4880.06</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10019,19 +10019,19 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2025NE0000677</t>
+          <t>2025NE0000675</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>14767.58</v>
+        <v>51146.86</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10049,19 +10049,19 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
+          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2025NE0000679</t>
+          <t>2025NE0000678</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>41829.02</v>
+        <v>5374.74</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10079,19 +10079,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2025NE0000678</t>
+          <t>2025NE0000679</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>5374.74</v>
+        <v>41829.02</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10109,19 +10109,19 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
+          <t>Contratação de empresa para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras–E-Obras para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2025NE0000675</t>
+          <t>2025NE0000677</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>51146.86</v>
+        <v>14767.58</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de acesso dedicado à internet com link de 100 Mbps e circuito de transmissão de dados ponto a ponto de 100 Mbps para esta SEINFRA. TC: 0051/2021 AD:</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2022NE0000021</t>
+          <t>2022NE0000037</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>11969.55</v>
+        <v>75588.67999999999</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10199,19 +10199,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Saldo do CT. n° 006/2018-SEINFRA, destinados a Prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus - SEINFRA.</t>
+          <t xml:space="preserve">Parte do Saldo do CT. Nº 042/2021-SEINFRA, destinados para prestação de serviços de hospedagem do Sistema Integrado de Controle de Obras Públicas - SICOP (e-Obras), para atender as necessidades desta </t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2022NE0000030</t>
+          <t>2022NE0000033</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>94202.24000000001</v>
+        <v>8378.879999999999</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10229,19 +10229,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. Nº051/2021-SEINFRA, destinados para acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrut</t>
+          <t xml:space="preserve">Parte do Saldo do CT. Nº 019/2019-SEINFRA, destinados para Contratação de Empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura </t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2022NE0000033</t>
+          <t>2022NE0000030</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>8378.879999999999</v>
+        <v>94202.24000000001</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10259,19 +10259,19 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do CT. Nº 019/2019-SEINFRA, destinados para Contratação de Empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura </t>
+          <t>Parte do Saldo do CT. Nº051/2021-SEINFRA, destinados para acesso à internet com link dedicado de 100Mbps e circuito de transmissão de dados pontos de 100Mbps para a Secretaria de Estado de Infraestrut</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2022NE0000037</t>
+          <t>2022NE0000021</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>75588.67999999999</v>
+        <v>11969.55</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10289,17 +10289,21 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte do Saldo do CT. Nº 042/2021-SEINFRA, destinados para prestação de serviços de hospedagem do Sistema Integrado de Controle de Obras Públicas - SICOP (e-Obras), para atender as necessidades desta </t>
+          <t>Saldo do CT. n° 006/2018-SEINFRA, destinados a Prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2019NE00942</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr"/>
+          <t>2019NE00943</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>6/2018</t>
+        </is>
+      </c>
       <c r="C332" t="inlineStr">
         <is>
           <t>02/10/2019</t>
@@ -10315,21 +10319,17 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Anulação da NE 00919 - em virtude da referência incorreta.</t>
+          <t>Parte Saldo do CT. N°006/2018, destinados à Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2019NE00943</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>6/2018</t>
-        </is>
-      </c>
+          <t>2019NE00942</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
           <t>02/10/2019</t>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Parte Saldo do CT. N°006/2018, destinados à Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
+          <t>Anulação da NE 00919 - em virtude da referência incorreta.</t>
         </is>
       </c>
     </row>
@@ -10494,12 +10494,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2025NE0000003</t>
+          <t>2025NE0000004</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10508,7 +10508,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>5374.74</v>
+        <v>14242.04</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
+          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -10554,12 +10554,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2025NE0000004</t>
+          <t>2025NE0000003</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>4/2023</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10568,7 +10568,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>14242.04</v>
+        <v>5374.74</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação dos serviços de Firewall para a Secretaria de Infraestrutura e Região Metropolitana de Manaus – SEINFRA. TC: 0004/2023 AD: 01.</t>
+          <t>Contratação de empresa especializada para prestação de serviço de licença de uso do sistema gestor de conteúdo web, para atender a Secretaria de Estado de Infraestrutura- SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -10614,12 +10614,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2023NE0000012</t>
+          <t>2023NE0000031</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>51/2021</t>
+          <t>41/2021</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>102293.72</v>
+        <v>5171.2</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10637,19 +10637,19 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. Nº051/2021-SEINFRA, destinados para serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta SEINFRA.</t>
+          <t>Parte do Saldo do CT. Nº041/2021-SEINFRA, destinados para prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2023NE0000007</t>
+          <t>2023NE0000033</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>42/2021</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>83658.03999999999</v>
+        <v>9607.24</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. Nº042/2021-SEINFRA, destinados para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras (E-Obras) para atender as necessidades da SEINFRA.</t>
+          <t>Parte do Saldo do CT. n°019/2019 - SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -10704,12 +10704,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2023NE0000033</t>
+          <t>2023NE0000007</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>42/2021</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>9607.24</v>
+        <v>83658.03999999999</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10727,19 +10727,19 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. n°019/2019 - SEINFRA, destinados a Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. Nº042/2021-SEINFRA, destinados para prestação de serviço de Hospedagem do Sistema Integrado de Controle e Gestão de Obras (E-Obras) para atender as necessidades da SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2023NE0000031</t>
+          <t>2023NE0000012</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>41/2021</t>
+          <t>51/2021</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>5171.2</v>
+        <v>102293.72</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10757,19 +10757,19 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. Nº041/2021-SEINFRA, destinados para prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB), para atender as necessidades</t>
+          <t>Parte do Saldo do CT. Nº051/2021-SEINFRA, destinados para serviços de acesso dedicado à Internet com link de 100Mbps e Circuito de Transmissão de Dados Ponto a Ponto de 100Mpbs, para esta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2020NE00009</t>
+          <t>2020NE00004</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>11106.69</v>
+        <v>51150.5</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10787,19 +10787,19 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados à Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Saldo do CT. N°009/2016 - SEINFRA, destinados à Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2020NE00018</t>
+          <t>2020NE00005</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10808,7 +10808,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>96881.28999999999</v>
+        <v>24055.92</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
+          <t>Saldo do CT. N°011/2016 - SEINFRA, destinados a Contratação de empresa para Prestação de serviços para aquisição do Programa de execução de sistema de Protocolo em Plataforma WEB (sproweb) para Secret</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2020NE00005</t>
+          <t>2020NE00018</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>24055.92</v>
+        <v>96881.28999999999</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10877,19 +10877,19 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°011/2016 - SEINFRA, destinados a Contratação de empresa para Prestação de serviços para aquisição do Programa de execução de sistema de Protocolo em Plataforma WEB (sproweb) para Secret</t>
+          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de Dados pontos de 10 MBPS.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2020NE00004</t>
+          <t>2020NE00009</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>51150.5</v>
+        <v>11106.69</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10907,19 +10907,19 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°009/2016 - SEINFRA, destinados à Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados à Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2019NE00007</t>
+          <t>2019NE00001</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2950.58</v>
+        <v>28524.03</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10937,21 +10937,17 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 001/2017-SEINFRA - Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2019NE00014</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>6/2018</t>
-        </is>
-      </c>
+          <t>2019NE00013</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
         <is>
           <t>02/01/2019</t>
@@ -10967,19 +10963,19 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 006/2018-SEINFRA - Prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de A</t>
+          <t>Anulação Total da NE N. 008/2019-SEINFRA, referente ao CT. 006/2018 em virtude de modalidade incorreta.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00008</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10988,7 +10984,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>26422.17</v>
+        <v>11382.33</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -10997,19 +10993,19 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 021/2016-SEINFRA - Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS.</t>
+          <t>Saldo do Contrato nº 006/2018-SEINFRA - Prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de A</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2019NE00009</t>
+          <t>2019NE00011</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>59/2018</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11018,7 +11014,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>6380.01</v>
+        <v>9020.969999999999</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11027,19 +11023,19 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação de Serviços Técnicos em informática de forma eventual para atender a necessidade da Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2019NE00011</t>
+          <t>2019NE00009</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>59/2018</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11048,7 +11044,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>9020.969999999999</v>
+        <v>6380.01</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11057,19 +11053,19 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Contratação de empresa para Prestação de Serviços Técnicos em informática de forma eventual para atender a necessidade da Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2019NE00008</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11078,7 +11074,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>11382.33</v>
+        <v>26422.17</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11087,17 +11083,21 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 006/2018-SEINFRA - Prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de A</t>
+          <t>Saldo do Contrato nº 021/2016-SEINFRA - Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2019NE00013</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr"/>
+          <t>2019NE00014</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>6/2018</t>
+        </is>
+      </c>
       <c r="C359" t="inlineStr">
         <is>
           <t>02/01/2019</t>
@@ -11113,19 +11113,19 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Anulação Total da NE N. 008/2019-SEINFRA, referente ao CT. 006/2018 em virtude de modalidade incorreta.</t>
+          <t>Saldo do Contrato nº 006/2018-SEINFRA - Prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de A</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2019NE00001</t>
+          <t>2019NE00007</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>28524.03</v>
+        <v>2950.58</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -11143,19 +11143,19 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo do Contrato nº 001/2017-SEINFRA - Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2018NE00055</t>
+          <t>2018NE00053</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>20186.95</v>
+        <v>36952.04</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11173,19 +11173,19 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do Contrato nº 009/2016-SEINFRA. Objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrad</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2018NE00057</t>
+          <t>2018NE00065</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>102740.99</v>
+        <v>16228.19</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11203,19 +11203,19 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Saldo co Contrato n° 021/2016, tendo como objeto: Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de dados pontos de 10 MBPS..</t>
+          <t>Termo Aditivo ao Contrato n° 001/2017 - Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2018NE00065</t>
+          <t>2018NE00057</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11224,7 +11224,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>16228.19</v>
+        <v>102740.99</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11233,19 +11233,19 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Termo Aditivo ao Contrato n° 001/2017 - Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para a Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Saldo co Contrato n° 021/2016, tendo como objeto: Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de dados pontos de 10 MBPS..</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2018NE00053</t>
+          <t>2018NE00055</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11254,7 +11254,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>36952.04</v>
+        <v>20186.95</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -11263,19 +11263,19 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Saldo do Contrato nº 009/2016-SEINFRA. Objeto: Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras SICOP ao Sistema de Administração Financeira Integrad</t>
+          <t>Parte do Saldo do CT. nº 011/2016-SEINFRA, tendo como objeto: Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2017NE00021</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>69944.24000000001</v>
+        <v>11535.4</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11293,19 +11293,19 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP.</t>
+          <t>Saldo do CT. N°011/2016 - Aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2017NE00017</t>
+          <t>2017NE00020</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>61/2012</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>13519.72</v>
+        <v>37360.36</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11323,19 +11323,19 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°061/2012 - SEINFRA, destinados a Contratação de serviços de locação de bens referente a equipamentos de informática, compreendendo a instalação e configuração de um Firewall UTM tipo 6,</t>
+          <t>Parte Saldo Contrato nº 021/2016-SEINFRA-Acesso a Internet SEINFRA</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2017NE00020</t>
+          <t>2017NE00017</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>61/2012</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>37360.36</v>
+        <v>13519.72</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11353,19 +11353,19 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Parte Saldo Contrato nº 021/2016-SEINFRA-Acesso a Internet SEINFRA</t>
+          <t>Saldo do CT. N°061/2012 - SEINFRA, destinados a Contratação de serviços de locação de bens referente a equipamentos de informática, compreendendo a instalação e configuração de um Firewall UTM tipo 6,</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00021</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>11535.4</v>
+        <v>69944.24000000001</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11383,19 +11383,19 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°011/2016 - Aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Parte do Saldo do CT. N°009/2016 - Prestação de Serviços para Hospedagem e Suporte ao Sistema Integrado de Controle de Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2014NE00379</t>
+          <t>2014NE00383</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>80/2009</t>
+          <t>30/2011</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11404,7 +11404,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>333372</v>
+        <v>14793.75</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Contrato No. 80/2009 - SICOP (Hospedagem, Acesso Internet, Suport Técnico)</t>
+          <t>Contrato No. 30/2011 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
@@ -11450,12 +11450,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2014NE00383</t>
+          <t>2014NE00379</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>30/2011</t>
+          <t>80/2009</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>14793.75</v>
+        <v>333372</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Contrato No. 30/2011 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 80/2009 - SICOP (Hospedagem, Acesso Internet, Suport Técnico)</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2017NE01082</t>
+          <t>2017NE01084</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Complementação do Saldo da NE n° 315/2017 referente ao CT nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manau</t>
+          <t>Complementação do Saldo da NE n° 315/2017 referente ao Contrato nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2017NE01084</t>
+          <t>2017NE01082</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11585,19 +11585,19 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Complementação do Saldo da NE n° 315/2017 referente ao Contrato nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários</t>
+          <t>Complementação do Saldo da NE n° 315/2017 referente ao CT nº 061/2012-SEINFRA, Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM tipo 6 para até 250 usuários Manau</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2019NE00917</t>
+          <t>2019NE00919</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>19/2019</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>4760.01</v>
+        <v>12150.63</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11615,19 +11615,19 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
+          <t>Saldo do CT. N°006/2018, destinados à Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2019NE00921</t>
+          <t>2019NE00920</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>30690.3</v>
+        <v>17614.78</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11645,19 +11645,19 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°009/2016 - SEINFRA, destinados à Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Contratação de empresa para Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS, nesta SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2019NE00920</t>
+          <t>2019NE00921</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>17614.78</v>
+        <v>30690.3</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11675,19 +11675,19 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°021/2016 - SEINFRA, destinados à Contratação de empresa para Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS, nesta SEINFRA.</t>
+          <t>Saldo do CT. N°009/2016 - SEINFRA, destinados à Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2019NE00919</t>
+          <t>2019NE00917</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>19/2019</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11696,7 +11696,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>12150.63</v>
+        <v>4760.01</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11705,17 +11705,21 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°006/2018, destinados à Prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com disponibilidade de Appliance (Conjunto de equipamento e software).</t>
+          <t>Saldo do CT. N°019/2019 - SEINFRA, destinados a Contratação de empresa para Prestação de Serviços de Uso do Sistema Gestão de Conteúdo Web, para esta Secretaria de Estado de Infraestrutura - SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2016NE00850</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr"/>
+          <t>2016NE00851</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>61/2012</t>
+        </is>
+      </c>
       <c r="C380" t="inlineStr">
         <is>
           <t>01/09/2016</t>
@@ -11731,21 +11735,17 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Anulação total NE N°845/2016, referente ao Contrato N°061/2012, em virtude de descrição incompleta.</t>
+          <t>Apostilamento ao Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2016NE00851</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>61/2012</t>
-        </is>
-      </c>
+          <t>2016NE00850</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
           <t>01/09/2016</t>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Apostilamento ao Contrato nº 061/2012-SEINFRA-Serviços de locação de bens, compreendendo a instalação e configuração de firewall UTM.</t>
+          <t>Anulação total NE N°845/2016, referente ao Contrato N°061/2012, em virtude de descrição incompleta.</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2018NE00755</t>
+          <t>2018NE00753</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11812,7 +11812,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>34965.64</v>
+        <v>134067.39</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°080/2009 - SEINFRA, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas, referente ao período de Julho/2015.</t>
+          <t>D.E.A ao CT. N°080/2009 - SEINFRA, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas, referente ao período de Dezembro/2015 a Abril/201</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2018NE00753</t>
+          <t>2018NE00755</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>134067.39</v>
+        <v>34965.64</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11881,19 +11881,19 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>D.E.A ao CT. N°080/2009 - SEINFRA, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas, referente ao período de Dezembro/2015 a Abril/201</t>
+          <t>D.E.A ao CT. N°080/2009 - SEINFRA, destinados a Implantação e Manutenção do Sistema Integrado e Gestão de Obras Públicas SICOP, no Estado do Amazonas, referente ao período de Julho/2015.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2019NE00550</t>
+          <t>2019NE00551</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>30690.3</v>
+        <v>6013.98</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11911,19 +11911,19 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Saldo do Contrato N° 009/2019-SEINFRA, Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
+          <t>Saldo Contrato n° 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2019NE00554</t>
+          <t>2019NE00552</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>6/2018</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>12150.63</v>
+        <v>26422.17</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Saldo do CT. N°006/18-SEINFRA, Contratação de empresa para prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com d</t>
+          <t>Saldo CT. 021/2016-SEINFRA - Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS, nesta SEINFRA.</t>
         </is>
       </c>
     </row>
@@ -11978,12 +11978,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2019NE00552</t>
+          <t>2019NE00554</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>6/2018</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>26422.17</v>
+        <v>12150.63</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -12001,19 +12001,19 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Saldo CT. 021/2016-SEINFRA - Acesso a Internet com link dedicado 06 MEGAS MBPS e Circuito de Tramissão de Dados ponto de 10 MBPS, nesta SEINFRA.</t>
+          <t>Saldo do CT. N°006/18-SEINFRA, Contratação de empresa para prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com d</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2019NE00551</t>
+          <t>2019NE00550</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6013.98</v>
+        <v>30690.3</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -12031,19 +12031,19 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Saldo Contrato n° 011/2016-SEINFRA - Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>Saldo do Contrato N° 009/2019-SEINFRA, Contratação de empresa para a Prestação de Serviços de Hospedagem do Sistema Integrado de Controle e Gestão de Obras - SICOP.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2018NE00207</t>
+          <t>2018NE00206</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2950.58</v>
+        <v>102740.99</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12061,19 +12061,19 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Saldo Contrato nº 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo Web para Secretaria de Estado de Infraestrutura - SEINFRA</t>
+          <t>Saldo Contrato n°021/2016-SEINFRA-Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de dados pontos de 10 MBPS.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2018NE00211</t>
+          <t>2018NE00210</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -12082,7 +12082,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>16228.19</v>
+        <v>20186.95</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12091,19 +12091,19 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo Contrato n° 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para SEINFRA.</t>
+          <t>Parte Saldo Contrato nº 011/2016-SEINFRA-Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2018NE00208</t>
+          <t>2018NE00212</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>21/2016</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>36952.04</v>
+        <v>9340.09</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -12121,19 +12121,19 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Saldo Contrato nº 009/2016-SEINFRA-Prestação de Serviços para Hospedagem e Suporte do SICOP ao AFI ao Sistema de Gestão PROSAMIM/SIGPRO.</t>
+          <t>Anulação Parcial da Nota de Empenho nº 206/2017 referente Contrato nº 021/2016-SEINFRA, devido ter sido empenhado a maior.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2018NE00212</t>
+          <t>2018NE00208</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>9340.09</v>
+        <v>36952.04</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -12151,19 +12151,19 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Anulação Parcial da Nota de Empenho nº 206/2017 referente Contrato nº 021/2016-SEINFRA, devido ter sido empenhado a maior.</t>
+          <t>Saldo Contrato nº 009/2016-SEINFRA-Prestação de Serviços para Hospedagem e Suporte do SICOP ao AFI ao Sistema de Gestão PROSAMIM/SIGPRO.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2018NE00210</t>
+          <t>2018NE00211</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>20186.95</v>
+        <v>16228.19</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -12181,19 +12181,19 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Parte Saldo Contrato nº 011/2016-SEINFRA-Prestação de serviços para aquisição do Programa de Execução de Sistema de Protocolo em Plataforma WEB (SPROWEB).</t>
+          <t>1º Termo Aditivo Contrato n° 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo WEB, para SEINFRA.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2018NE00206</t>
+          <t>2018NE00207</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>21/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>102740.99</v>
+        <v>2950.58</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Saldo Contrato n°021/2016-SEINFRA-Acesso a Internet com Link dedicado 06 (seis) MBPS e Circuito de Transmissão de dados pontos de 10 MBPS.</t>
+          <t>Saldo Contrato nº 001/2017-SEINFRA-Serviços de licença de uso do Sistema Gestor de Conteúdo Web para Secretaria de Estado de Infraestrutura - SEINFRA</t>
         </is>
       </c>
     </row>
